--- a/docs/sprintreviews/product-backlog.xlsx
+++ b/docs/sprintreviews/product-backlog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ostap\School_Files\Year_3\room-food\docs\sprintreviews\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A021406-F0E9-4920-A379-8B85A485A8EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13494E00-7986-4489-A457-F43844174879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
   <si>
     <t>#</t>
   </si>
@@ -124,12 +124,20 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₴&quot;_-;\-* #,##0.00\ &quot;₴&quot;_-;_-* &quot;-&quot;??\ &quot;₴&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -191,39 +199,39 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -650,8 +658,8 @@
       <c r="D8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="12">
-        <v>0.8</v>
+      <c r="E8" s="12" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -667,8 +675,8 @@
       <c r="D9" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="12">
-        <v>0.9</v>
+      <c r="E9" s="12" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
